--- a/resources/quality_schema_data_quality_anthropometric_template.xlsx
+++ b/resources/quality_schema_data_quality_anthropometric_template.xlsx
@@ -1,34 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4586C9-C838-4B75-9DEF-D59FA2404C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality Checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+  <si>
+    <t>check_group</t>
+  </si>
+  <si>
+    <t>check_name</t>
+  </si>
+  <si>
+    <t>MUAC</t>
+  </si>
+  <si>
+    <t>plaus_ageratio</t>
+  </si>
+  <si>
+    <t>plaus_sexratio</t>
+  </si>
+  <si>
+    <t>plaus_dps_muac</t>
+  </si>
+  <si>
+    <t>plaus_perc_mfaz_children</t>
+  </si>
+  <si>
+    <t>plaus_n_children_muac</t>
+  </si>
+  <si>
+    <t>plaus_sd_muac_mm</t>
+  </si>
+  <si>
+    <t>check_label</t>
+  </si>
+  <si>
+    <t>variables</t>
+  </si>
+  <si>
+    <t>statistical_test</t>
+  </si>
+  <si>
+    <t>threshold_expression</t>
+  </si>
+  <si>
+    <t>penalty_score</t>
+  </si>
+  <si>
+    <t>test_params</t>
+  </si>
+  <si>
+    <t>p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt; 0.05 &amp; p_value &lt;= 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt; 0.001 &amp; p_value &lt;= 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt;= 0.001</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>num_children_6_29m,num_children_30_59m</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 8</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 8 &amp; test_statistic &lt; 13</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 13 &amp; test_statistic &lt; 20</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 20</t>
+  </si>
+  <si>
+    <t>nut_muac_cm</t>
+  </si>
+  <si>
+    <t>flag_sd_mfaz</t>
+  </si>
+  <si>
+    <t>ageratio</t>
+  </si>
+  <si>
+    <t>sexratio</t>
+  </si>
+  <si>
+    <t>digit_preference</t>
+  </si>
+  <si>
+    <t>flag_percentage</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>nut_muac_mm</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 1 &amp; test_statistic &lt; 3</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 3 &amp; test_statistic &lt; 5</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 5</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 12</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 12 &amp; test_statistic &lt; 14</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 14 &amp; test_statistic &lt; 16</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 16</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 100</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 80 &amp; test_statistic &lt; 100</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 50 &amp; test_statistic &lt; 80</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 50</t>
+  </si>
+  <si>
+    <t>Age Ratio 6-29m : 30-59m</t>
+  </si>
+  <si>
+    <t>Sex Ratio</t>
+  </si>
+  <si>
+    <t>Digit Preference Score (MUAC)</t>
+  </si>
+  <si>
+    <t>% SMART Flags MFAZ</t>
+  </si>
+  <si>
+    <t>Standard Deviation MUAC mm</t>
+  </si>
+  <si>
+    <t>Number of Children Measured</t>
+  </si>
+  <si>
+    <t>flag_value = 1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Cascadia Code Light"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +220,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,168 +526,611 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.7109375" customWidth="1"/>
+    <col min="7" max="7" width="58.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>check_group</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>check_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>check_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>check_type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>anthro_01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Weight plausibility</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>plausibility</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>weight_kg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>weight_kg &gt; 2 &amp; weight_kg &lt; 40</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Weight should be between 2kg and 40kg for children</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>anthro_02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Height plausibility</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>plausibility</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>height_cm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>height_cm &gt; 45 &amp; height_cm &lt; 120</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Height should be between 45cm and 120cm for children under 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>anthro_03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MUAC plausibility</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>plausibility</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>muac_mm</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>muac_mm &gt; 80 &amp; muac_mm &lt; 250</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>MUAC should be between 80mm and 250mm</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resources/quality_schema_data_quality_anthropometric_template.xlsx
+++ b/resources/quality_schema_data_quality_anthropometric_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4586C9-C838-4B75-9DEF-D59FA2404C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889D629A-2CD6-40E4-980D-522CA2E62192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14820" yWindow="0" windowWidth="14475" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
   <si>
     <t>check_group</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>flag_value = 1</t>
+  </si>
+  <si>
+    <t>male_value = @value_map$sex$male,female_value=@value_map$sex@female,expected_ratio_val=1</t>
+  </si>
+  <si>
+    <t>yes_val=1,no_val=0,expected_ratio_val=0.85</t>
   </si>
 </sst>
 </file>
@@ -587,6 +593,9 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -610,6 +619,9 @@
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -633,6 +645,9 @@
       <c r="G4">
         <v>3</v>
       </c>
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -656,6 +671,9 @@
       <c r="G5">
         <v>5</v>
       </c>
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -679,6 +697,9 @@
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -702,6 +723,9 @@
       <c r="G7">
         <v>1</v>
       </c>
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -725,6 +749,9 @@
       <c r="G8">
         <v>3</v>
       </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -747,6 +774,9 @@
       </c>
       <c r="G9">
         <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">

--- a/resources/quality_schema_data_quality_anthropometric_template.xlsx
+++ b/resources/quality_schema_data_quality_anthropometric_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889D629A-2CD6-40E4-980D-522CA2E62192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A61E76D-FD96-4102-91E2-5CDB68417242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14820" yWindow="0" windowWidth="14475" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -181,10 +181,10 @@
     <t>flag_value = 1</t>
   </si>
   <si>
-    <t>male_value = @value_map$sex$male,female_value=@value_map$sex@female,expected_ratio_val=1</t>
-  </si>
-  <si>
     <t>yes_val=1,no_val=0,expected_ratio_val=0.85</t>
+  </si>
+  <si>
+    <t>male_value = @value_map$sex$male,female_value=@value_map$sex$female,expected_ratio_val=1</t>
   </si>
 </sst>
 </file>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -620,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -646,7 +646,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -750,7 +750,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -776,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">

--- a/resources/quality_schema_data_quality_anthropometric_template.xlsx
+++ b/resources/quality_schema_data_quality_anthropometric_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A61E76D-FD96-4102-91E2-5CDB68417242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C338E92C-715B-454A-ADE8-C01C27817F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5865" yWindow="5115" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
     <t>yes_val=1,no_val=0,expected_ratio_val=0.85</t>
   </si>
   <si>
-    <t>male_value = @value_map$sex$male,female_value=@value_map$sex$female,expected_ratio_val=1</t>
+    <t>male_val = @value_map$sex$male,female_val=@value_map$sex$female,expected_ratio_val=1</t>
   </si>
 </sst>
 </file>
